--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.03995122295376</v>
+        <v>6.506492073729986</v>
       </c>
       <c r="D2" t="n">
-        <v>13.78363747823916</v>
+        <v>2.239841090213864</v>
       </c>
       <c r="E2" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F2" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.80824318163085</v>
+        <v>6.143839517015014</v>
       </c>
       <c r="D3" t="n">
-        <v>37.15572697629167</v>
+        <v>6.037805633647397</v>
       </c>
       <c r="E3" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F3" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.07750142182777</v>
+        <v>5.375093981047013</v>
       </c>
       <c r="D4" t="n">
-        <v>2.768976988003097</v>
+        <v>0.4499587605505032</v>
       </c>
       <c r="E4" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F4" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.10980722066041</v>
+        <v>6.517843673357318</v>
       </c>
       <c r="D5" t="n">
-        <v>22.93727093061993</v>
+        <v>3.727306526225739</v>
       </c>
       <c r="E5" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F5" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.46726372606293</v>
+        <v>4.463430355485226</v>
       </c>
       <c r="D6" t="n">
-        <v>26.81325819365803</v>
+        <v>4.357154456469431</v>
       </c>
       <c r="E6" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F6" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.89977042155178</v>
+        <v>5.671212693502164</v>
       </c>
       <c r="D7" t="n">
-        <v>30.6514676917</v>
+        <v>4.98086349990125</v>
       </c>
       <c r="E7" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F7" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.21478141486262</v>
+        <v>4.422401979915176</v>
       </c>
       <c r="D8" t="n">
-        <v>26.9785114959102</v>
+        <v>4.384008118085408</v>
       </c>
       <c r="E8" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F8" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.37161882651721</v>
+        <v>4.122888059309047</v>
       </c>
       <c r="D9" t="n">
-        <v>25.37970443794844</v>
+        <v>4.124201971166621</v>
       </c>
       <c r="E9" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F9" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.32337094492275</v>
+        <v>2.815047778549947</v>
       </c>
       <c r="D10" t="n">
-        <v>17.65526590421883</v>
+        <v>2.86898070943556</v>
       </c>
       <c r="E10" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F10" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.36591750635473</v>
+        <v>5.259461594782644</v>
       </c>
       <c r="D11" t="n">
-        <v>32.55495947553334</v>
+        <v>5.290180914774168</v>
       </c>
       <c r="E11" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F11" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.29133574706281</v>
+        <v>2.972342058897707</v>
       </c>
       <c r="D12" t="n">
-        <v>18.91779203280118</v>
+        <v>3.074141205330192</v>
       </c>
       <c r="E12" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F12" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.48553005003195</v>
+        <v>3.816398633130191</v>
       </c>
       <c r="D13" t="n">
-        <v>23.82234141779729</v>
+        <v>3.87113048039206</v>
       </c>
       <c r="E13" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F13" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.60915756757889</v>
+        <v>6.27398810473157</v>
       </c>
       <c r="D14" t="n">
-        <v>38.92211137166415</v>
+        <v>6.324843097895425</v>
       </c>
       <c r="E14" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F14" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.03289697141808</v>
+        <v>4.392845757855437</v>
       </c>
       <c r="D15" t="n">
-        <v>26.81460849626841</v>
+        <v>4.357373880643616</v>
       </c>
       <c r="E15" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F15" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>32.05032435945193</v>
+        <v>5.208177708410939</v>
       </c>
       <c r="D16" t="n">
-        <v>32.45732944293047</v>
+        <v>5.274316034476202</v>
       </c>
       <c r="E16" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F16" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.44731116637388</v>
+        <v>6.085188064535756</v>
       </c>
       <c r="D17" t="n">
-        <v>37.84094680772419</v>
+        <v>6.149153856255182</v>
       </c>
       <c r="E17" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F17" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>15.19005142219597</v>
+        <v>2.468383356106846</v>
       </c>
       <c r="D18" t="n">
-        <v>15.00852959475516</v>
+        <v>2.438886059147714</v>
       </c>
       <c r="E18" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F18" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31.40226685319383</v>
+        <v>5.102868363643997</v>
       </c>
       <c r="D19" t="n">
-        <v>34.2321940348566</v>
+        <v>5.562731530664197</v>
       </c>
       <c r="E19" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F19" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>15.0955600836718</v>
+        <v>2.453028513596668</v>
       </c>
       <c r="D20" t="n">
-        <v>17.89398215788065</v>
+        <v>2.907772100655605</v>
       </c>
       <c r="E20" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F20" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>46.85328366454919</v>
+        <v>7.613658595489244</v>
       </c>
       <c r="D21" t="n">
-        <v>47.46376627579854</v>
+        <v>7.712862019817263</v>
       </c>
       <c r="E21" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F21" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>41.50157306583857</v>
+        <v>6.744005623198768</v>
       </c>
       <c r="D22" t="n">
-        <v>38.89545038076299</v>
+        <v>6.320510686873987</v>
       </c>
       <c r="E22" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F22" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>14.89617744889987</v>
+        <v>2.420628835446229</v>
       </c>
       <c r="D23" t="n">
-        <v>12.13961521084732</v>
+        <v>1.97268747176269</v>
       </c>
       <c r="E23" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F23" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>4.102951249475347</v>
+        <v>0.666729578039744</v>
       </c>
       <c r="D24" t="n">
-        <v>5.943543244224629</v>
+        <v>0.9658257771865022</v>
       </c>
       <c r="E24" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F24" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>30.1328547987119</v>
+        <v>4.896588904790684</v>
       </c>
       <c r="D25" t="n">
-        <v>32.65372209497519</v>
+        <v>5.30622984043347</v>
       </c>
       <c r="E25" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F25" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>14.00406767250786</v>
+        <v>2.275660996782528</v>
       </c>
       <c r="D26" t="n">
-        <v>16.06364730952621</v>
+        <v>2.610342687798009</v>
       </c>
       <c r="E26" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F26" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>50.69727376458435</v>
+        <v>8.238306986744956</v>
       </c>
       <c r="D27" t="n">
-        <v>53.1695820205934</v>
+        <v>8.640057078346427</v>
       </c>
       <c r="E27" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F27" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>34.86316146448709</v>
+        <v>5.665263737979153</v>
       </c>
       <c r="D28" t="n">
-        <v>32.06010859214606</v>
+        <v>5.209767646223734</v>
       </c>
       <c r="E28" t="n">
-        <v>11.01349225127457</v>
+        <v>1.789692490832118</v>
       </c>
       <c r="F28" t="n">
-        <v>11.77515154217089</v>
+        <v>1.913462125602769</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
